--- a/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3813" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3812" uniqueCount="648">
   <si>
     <t>Property</t>
   </si>
@@ -975,9 +975,6 @@
   </si>
   <si>
     <t>このMedicationRequestオーダの優先度。他のオーダと比較して表現される。</t>
-  </si>
-  <si>
-    <t>FHIRでは文字列の大きさが1MBを超えてはならない(SHALL NOT)。</t>
   </si>
   <si>
     <t>リクエストの実行に割り当てられる重要性のレベルを特定します。 / Identifies the level of importance to be assigned to actioning the request.</t>
@@ -7371,9 +7368,7 @@
       <c r="M43" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="N43" t="s" s="2">
-        <v>306</v>
-      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7401,10 +7396,10 @@
         <v>185</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7437,16 +7432,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AL43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7454,10 +7449,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7480,16 +7475,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7539,7 +7534,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7560,7 +7555,7 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
@@ -7571,10 +7566,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7597,13 +7592,13 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7654,7 +7649,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7675,7 +7670,7 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7686,10 +7681,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7712,16 +7707,16 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7771,7 +7766,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>91</v>
@@ -7786,27 +7781,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>332</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7829,16 +7824,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7888,7 +7883,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>91</v>
@@ -7903,27 +7898,27 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AM47" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>342</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7946,16 +7941,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8005,7 +8000,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8020,27 +8015,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>276</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8063,16 +8058,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8122,7 +8117,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8137,16 +8132,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>358</v>
-      </c>
       <c r="AN49" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8154,10 +8149,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8180,13 +8175,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8237,7 +8232,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8252,27 +8247,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>367</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8295,16 +8290,16 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>371</v>
-      </c>
       <c r="N51" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8354,7 +8349,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8369,16 +8364,16 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8386,10 +8381,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8412,16 +8407,16 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>377</v>
-      </c>
       <c r="N52" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8471,7 +8466,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8486,16 +8481,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8503,10 +8498,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8532,13 +8527,13 @@
         <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8568,7 +8563,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8586,7 +8581,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8601,13 +8596,13 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8618,10 +8613,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8644,16 +8639,16 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="N54" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8703,7 +8698,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8724,10 +8719,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8735,10 +8730,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8764,13 +8759,13 @@
         <v>192</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8799,11 +8794,11 @@
         <v>282</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>399</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8820,7 +8815,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8835,27 +8830,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>404</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8878,16 +8873,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8937,7 +8932,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8952,16 +8947,16 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>276</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8969,10 +8964,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8995,16 +8990,16 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9054,7 +9049,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9069,13 +9064,13 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -9086,10 +9081,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9115,13 +9110,13 @@
         <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9171,7 +9166,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9192,7 +9187,7 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
@@ -9203,10 +9198,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9229,16 +9224,16 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>425</v>
-      </c>
       <c r="N59" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9288,7 +9283,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9303,13 +9298,13 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -9320,10 +9315,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9349,14 +9344,14 @@
         <v>149</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9405,7 +9400,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9420,13 +9415,13 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
@@ -9437,10 +9432,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9466,13 +9461,13 @@
         <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9501,11 +9496,11 @@
         <v>282</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9522,7 +9517,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9543,7 +9538,7 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
@@ -9554,10 +9549,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9580,16 +9575,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="M62" t="s" s="2">
-        <v>444</v>
-      </c>
       <c r="N62" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9639,7 +9634,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9654,13 +9649,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9671,10 +9666,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9697,16 +9692,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9756,7 +9751,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9771,13 +9766,13 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
@@ -9788,10 +9783,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9814,16 +9809,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9873,7 +9868,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9888,13 +9883,13 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
@@ -9905,10 +9900,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9931,13 +9926,13 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9988,7 +9983,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10006,10 +10001,10 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
@@ -10020,10 +10015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10049,10 +10044,10 @@
         <v>168</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10135,10 +10130,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10164,10 +10159,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10248,13 +10243,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C68" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>82</v>
@@ -10276,13 +10271,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10342,7 +10337,7 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>142</v>
@@ -10365,13 +10360,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C69" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
@@ -10393,13 +10388,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10459,7 +10454,7 @@
         <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>142</v>
@@ -10482,14 +10477,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10511,10 +10506,10 @@
         <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>140</v>
@@ -10569,7 +10564,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10601,10 +10596,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10627,16 +10622,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10686,7 +10681,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10707,7 +10702,7 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10718,10 +10713,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10833,10 +10828,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10950,14 +10945,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10979,10 +10974,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -11037,7 +11032,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11069,10 +11064,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11095,16 +11090,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11154,7 +11149,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11175,7 +11170,7 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
@@ -11186,10 +11181,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11212,16 +11207,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="M76" t="s" s="2">
-        <v>507</v>
-      </c>
       <c r="N76" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11271,7 +11266,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11292,7 +11287,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11303,10 +11298,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11329,16 +11324,16 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M77" t="s" s="2">
-        <v>511</v>
-      </c>
       <c r="N77" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11388,7 +11383,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11409,7 +11404,7 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11420,10 +11415,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11449,16 +11444,16 @@
         <v>222</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11507,7 +11502,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11525,10 +11520,10 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11539,10 +11534,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11654,10 +11649,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11771,10 +11766,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11797,16 +11792,16 @@
         <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11856,16 +11851,16 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI81" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>103</v>
@@ -11877,21 +11872,21 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>528</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11914,69 +11909,69 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q82" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="R82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="R82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>534</v>
-      </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
@@ -11984,7 +11979,7 @@
         <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>103</v>
@@ -11996,21 +11991,21 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO82" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>536</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12033,16 +12028,16 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12092,7 +12087,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12110,24 +12105,24 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AN83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO83" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>544</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12150,16 +12145,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="M84" t="s" s="2">
-        <v>547</v>
-      </c>
       <c r="N84" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12209,7 +12204,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12227,24 +12222,24 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="AM84" t="s" s="2">
+      <c r="AN84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>550</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12267,16 +12262,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12326,7 +12321,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12344,10 +12339,10 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12358,10 +12353,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12473,10 +12468,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12590,10 +12585,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12616,19 +12611,19 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12677,7 +12672,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12698,21 +12693,21 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO88" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>567</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12738,20 +12733,20 @@
         <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q89" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="P89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q89" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="R89" t="s" s="2">
         <v>82</v>
@@ -12775,28 +12770,28 @@
         <v>185</v>
       </c>
       <c r="Y89" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="Z89" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="Z89" t="s" s="2">
+      <c r="AA89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF89" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12817,21 +12812,21 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO89" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>577</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12857,63 +12852,63 @@
         <v>168</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12934,21 +12929,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>585</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12974,72 +12969,72 @@
         <v>105</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="S91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF91" t="s" s="2">
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI91" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13051,21 +13046,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13091,65 +13086,65 @@
         <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13170,21 +13165,21 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13207,16 +13202,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="M93" t="s" s="2">
-        <v>605</v>
-      </c>
       <c r="N93" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13266,7 +13261,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13287,10 +13282,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13298,10 +13293,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13324,13 +13319,13 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13381,7 +13376,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13399,10 +13394,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13413,10 +13408,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13528,10 +13523,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13645,14 +13640,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13674,10 +13669,10 @@
         <v>137</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>140</v>
@@ -13732,7 +13727,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13764,10 +13759,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13793,13 +13788,13 @@
         <v>192</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="M98" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="N98" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13829,7 +13824,7 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13847,7 +13842,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>91</v>
@@ -13865,24 +13860,24 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO98" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>620</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13908,13 +13903,13 @@
         <v>192</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13944,7 +13939,7 @@
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -13962,7 +13957,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13980,24 +13975,24 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AM99" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="AM99" t="s" s="2">
+      <c r="AN99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO99" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>628</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14020,16 +14015,16 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="M100" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="M100" t="s" s="2">
-        <v>632</v>
-      </c>
       <c r="N100" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14079,7 +14074,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14094,13 +14089,13 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AM100" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
@@ -14111,14 +14106,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14137,16 +14132,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14196,7 +14191,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14217,7 +14212,7 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
@@ -14228,10 +14223,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14254,16 +14249,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14313,7 +14308,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14328,13 +14323,13 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM102" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>82</v>
